--- a/17 18 20/2 Tableau/5.Calculations/5.Data/DataCleaning.xlsx
+++ b/17 18 20/2 Tableau/5.Calculations/5.Data/DataCleaning.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="130">
   <si>
     <t>Customer ID</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>Sum of Sales</t>
+  </si>
+  <si>
+    <t>Running Total</t>
   </si>
 </sst>
 </file>
@@ -425,7 +428,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -550,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -951,7 +954,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1081,7 +1084,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1211,7 +1214,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1341,7 +1344,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -1471,7 +1474,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -2789,6 +2792,9 @@
       <c r="B3" t="s">
         <v>128</v>
       </c>
+      <c r="E3" s="13" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
@@ -3075,10 +3081,6 @@
       <c r="B4" s="12">
         <v>25</v>
       </c>
-      <c r="E4" s="13">
-        <f>SUM($B$4:B4)</f>
-        <v>25</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
@@ -3367,7 +3369,7 @@
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13">
-        <f>((B5/$B$23)*100)</f>
+        <f t="shared" ref="E4:E20" si="0">((B5/$B$23)*100)</f>
         <v>0.42028579434015129</v>
       </c>
     </row>
@@ -3380,7 +3382,7 @@
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13">
-        <f>((B6/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>0.49033342673017655</v>
       </c>
     </row>
@@ -3393,7 +3395,7 @@
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13">
-        <f>((B7/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>0.56038105912020175</v>
       </c>
     </row>
@@ -3406,7 +3408,7 @@
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13">
-        <f>((B8/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>0.63042869151022696</v>
       </c>
     </row>
@@ -3419,7 +3421,7 @@
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13">
-        <f>((B9/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>0.77052395629027737</v>
       </c>
     </row>
@@ -3432,7 +3434,7 @@
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13">
-        <f>((B10/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>1.0507144858503783</v>
       </c>
     </row>
@@ -3445,7 +3447,7 @@
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13">
-        <f>((B11/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>1.3309050154104791</v>
       </c>
     </row>
@@ -3458,7 +3460,7 @@
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13">
-        <f>((B12/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>1.6811431773606051</v>
       </c>
     </row>
@@ -3471,7 +3473,7 @@
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13">
-        <f>((B13/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>4.483048472961614</v>
       </c>
     </row>
@@ -3484,7 +3486,7 @@
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13">
-        <f>((B14/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>5.3236200616419165</v>
       </c>
     </row>
@@ -3497,7 +3499,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13">
-        <f>((B15/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>6.3042869151022698</v>
       </c>
     </row>
@@ -3510,7 +3512,7 @@
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13">
-        <f>((B16/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>7.0047632390025223</v>
       </c>
     </row>
@@ -3523,7 +3525,7 @@
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13">
-        <f>((B17/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>8.4057158868030264</v>
       </c>
     </row>
@@ -3536,7 +3538,7 @@
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13">
-        <f>((B18/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>9.1061922107032789</v>
       </c>
     </row>
@@ -3549,7 +3551,7 @@
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13">
-        <f>((B19/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>9.8066685346035296</v>
       </c>
     </row>
@@ -3562,7 +3564,7 @@
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13">
-        <f>((B20/$B$23)*100)</f>
+        <f t="shared" si="0"/>
         <v>12.160268982908377</v>
       </c>
     </row>
@@ -3575,7 +3577,7 @@
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13">
-        <f t="shared" ref="E21:E23" si="0">((B21/$B$23)*100)</f>
+        <f t="shared" ref="E21:E22" si="1">((B21/$B$23)*100)</f>
         <v>13.30905015410479</v>
       </c>
     </row>
@@ -3588,7 +3590,7 @@
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.811431773606053</v>
       </c>
     </row>
@@ -3665,7 +3667,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="14">
-        <f t="shared" ref="D6:D22" si="0">(B6-B5)/B5</f>
+        <f>(B6-B5)/B5</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="G6">
@@ -3681,7 +3683,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D6:D22" si="0">(B7-B6)/B6</f>
         <v>0.14285714285714285</v>
       </c>
     </row>
